--- a/formato/MEDICINA 10-02-2026v2.xlsx
+++ b/formato/MEDICINA 10-02-2026v2.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/juanquezada/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/juanquezada/Downloads/cotizador_pdf_app/formato/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C836082F-427D-D948-9043-D8E8D68E3742}" xr6:coauthVersionLast="38" xr6:coauthVersionMax="38" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F2542B7-BFA2-254E-B8CC-F260F9E1A9BA}" xr6:coauthVersionLast="38" xr6:coauthVersionMax="38" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <r>
       <rPr>
@@ -66,22 +66,10 @@
     </r>
   </si>
   <si>
-    <t>Agua destilada inyectable 1 lt</t>
-  </si>
-  <si>
-    <t>Aguja hipodérmica N° 18</t>
-  </si>
-  <si>
-    <t>Aguja hipodérmica N° 20</t>
-  </si>
-  <si>
     <t>P.U.</t>
   </si>
   <si>
     <t xml:space="preserve">Abbocath N°20 </t>
-  </si>
-  <si>
-    <t>Abbocath N°22</t>
   </si>
 </sst>
 </file>
@@ -114,7 +102,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -125,12 +113,6 @@
       <patternFill patternType="solid">
         <fgColor theme="0"/>
         <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -183,12 +165,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -210,9 +189,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -561,136 +537,72 @@
   <dimension ref="A1:F262"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.3984375" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="2.19921875" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="4.19921875" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="115" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5.796875" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.19921875" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="5.19921875" style="2" customWidth="1"/>
-    <col min="8" max="16384" width="9.3984375" style="2"/>
+    <col min="1" max="1" width="2.19921875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="4.19921875" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="115" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.796875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.19921875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="5.19921875" style="1" customWidth="1"/>
+    <col min="8" max="16384" width="9.3984375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" s="6" t="s">
+      <c r="E1" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="5" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="2">
+      <c r="A2" s="1">
         <v>1</v>
       </c>
-      <c r="B2" s="6">
+      <c r="B2" s="5">
         <v>1</v>
       </c>
-      <c r="C2" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" s="5">
+      <c r="C2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" s="4">
         <v>50</v>
       </c>
-      <c r="E2" s="6">
+      <c r="E2" s="5">
         <v>2.5</v>
       </c>
-      <c r="F2" s="6">
+      <c r="F2" s="5">
         <f>D2*E2</f>
         <v>125</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="2">
+      <c r="A3" s="1">
         <v>1</v>
       </c>
-      <c r="B3" s="6">
-        <v>2</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3" s="5">
-        <v>50</v>
-      </c>
-      <c r="E3" s="6">
-        <v>2.5</v>
-      </c>
-      <c r="F3" s="6">
-        <f t="shared" ref="F3:F6" si="0">D3*E3</f>
-        <v>125</v>
-      </c>
     </row>
     <row r="4" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="2">
+      <c r="A4" s="1">
         <v>1</v>
       </c>
-      <c r="B4" s="6">
-        <v>3</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="D4" s="5">
-        <v>10</v>
-      </c>
-      <c r="E4" s="6">
-        <v>7</v>
-      </c>
-      <c r="F4" s="6">
-        <f t="shared" si="0"/>
-        <v>70</v>
-      </c>
     </row>
     <row r="5" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="2">
+      <c r="A5" s="1">
         <v>1</v>
       </c>
-      <c r="B5" s="6">
-        <v>4</v>
-      </c>
-      <c r="C5" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="D5" s="1">
-        <v>100</v>
-      </c>
-      <c r="E5" s="6">
-        <v>0.06</v>
-      </c>
-      <c r="F5" s="6">
-        <f t="shared" si="0"/>
-        <v>6</v>
-      </c>
     </row>
     <row r="6" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="2">
+      <c r="A6" s="1">
         <v>1</v>
-      </c>
-      <c r="B6" s="6">
-        <v>5</v>
-      </c>
-      <c r="C6" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="D6" s="1">
-        <v>100</v>
-      </c>
-      <c r="E6" s="6">
-        <v>0.06</v>
-      </c>
-      <c r="F6" s="6">
-        <f t="shared" si="0"/>
-        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
@@ -740,133 +652,134 @@
     <row r="62" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="63" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="64" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="65" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="68" ht="29.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="69" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="70" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="71" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="72" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="73" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="74" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="80" ht="33" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="81" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="83" spans="2:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="65" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="68" spans="2:3" ht="29.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="69" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="70" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="71" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="72" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="73" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="74" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="80" spans="2:3" ht="33" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B80" s="9"/>
+      <c r="C80" s="2"/>
+    </row>
+    <row r="81" spans="2:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B81" s="9"/>
+      <c r="C81" s="2"/>
+    </row>
+    <row r="82" spans="2:3" x14ac:dyDescent="0.15">
+      <c r="B82" s="9"/>
+      <c r="C82" s="2"/>
+    </row>
+    <row r="83" spans="2:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B83" s="9"/>
+      <c r="C83" s="2"/>
+    </row>
     <row r="84" spans="2:3" ht="16" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B84" s="11"/>
-      <c r="C84" s="3"/>
+      <c r="B84" s="9"/>
+      <c r="C84" s="2"/>
     </row>
     <row r="85" spans="2:3" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B85" s="11"/>
-      <c r="C85" s="3"/>
+      <c r="B85" s="9"/>
+      <c r="C85" s="2"/>
     </row>
     <row r="86" spans="2:3" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B86" s="11"/>
-      <c r="C86" s="3"/>
+      <c r="B86" s="9"/>
+      <c r="C86" s="2"/>
     </row>
     <row r="87" spans="2:3" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B87" s="11"/>
-      <c r="C87" s="3"/>
+      <c r="B87" s="9"/>
+      <c r="C87" s="2"/>
     </row>
     <row r="88" spans="2:3" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B88" s="11"/>
-      <c r="C88" s="3"/>
+      <c r="B88" s="9"/>
+      <c r="C88" s="2"/>
     </row>
     <row r="89" spans="2:3" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B89" s="11"/>
-      <c r="C89" s="3"/>
+      <c r="B89" s="9"/>
+      <c r="C89" s="2"/>
     </row>
     <row r="90" spans="2:3" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B90" s="11"/>
-      <c r="C90" s="3"/>
+      <c r="B90" s="9"/>
+      <c r="C90" s="2"/>
     </row>
     <row r="91" spans="2:3" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B91" s="11"/>
-      <c r="C91" s="3"/>
+      <c r="B91" s="9"/>
+      <c r="C91" s="2"/>
     </row>
     <row r="92" spans="2:3" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B92" s="11"/>
-      <c r="C92" s="3"/>
+      <c r="B92" s="9"/>
+      <c r="C92" s="2"/>
     </row>
     <row r="93" spans="2:3" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B93" s="11"/>
-      <c r="C93" s="3"/>
+      <c r="B93" s="9"/>
+      <c r="C93" s="2"/>
     </row>
     <row r="94" spans="2:3" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B94" s="11"/>
-      <c r="C94" s="3"/>
+      <c r="B94" s="9"/>
+      <c r="C94" s="2"/>
     </row>
     <row r="95" spans="2:3" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B95" s="11"/>
-      <c r="C95" s="3"/>
+      <c r="B95" s="9"/>
+      <c r="C95" s="2"/>
     </row>
     <row r="96" spans="2:3" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B96" s="11"/>
-      <c r="C96" s="3"/>
+      <c r="B96" s="9"/>
+      <c r="C96" s="2"/>
     </row>
     <row r="97" spans="2:3" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B97" s="11"/>
-      <c r="C97" s="3"/>
+      <c r="B97" s="9"/>
+      <c r="C97" s="2"/>
     </row>
     <row r="98" spans="2:3" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B98" s="11"/>
-      <c r="C98" s="3"/>
+      <c r="B98" s="9"/>
+      <c r="C98" s="2"/>
     </row>
     <row r="99" spans="2:3" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B99" s="11"/>
-      <c r="C99" s="3"/>
+      <c r="B99" s="9"/>
+      <c r="C99" s="8"/>
     </row>
     <row r="100" spans="2:3" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B100" s="11"/>
-      <c r="C100" s="3"/>
+      <c r="B100" s="9"/>
+      <c r="C100" s="8"/>
     </row>
     <row r="101" spans="2:3" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B101" s="11"/>
-      <c r="C101" s="3"/>
+      <c r="B101" s="9"/>
+      <c r="C101" s="2"/>
     </row>
     <row r="102" spans="2:3" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B102" s="11"/>
-      <c r="C102" s="3"/>
+      <c r="B102" s="9"/>
+      <c r="C102" s="2"/>
     </row>
     <row r="103" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B103" s="11"/>
-      <c r="C103" s="10"/>
+      <c r="B103" s="9"/>
+      <c r="C103" s="2"/>
     </row>
     <row r="104" spans="2:3" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B104" s="11"/>
-      <c r="C104" s="10"/>
+      <c r="B104" s="9"/>
+      <c r="C104" s="2"/>
     </row>
     <row r="105" spans="2:3" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B105" s="11"/>
-      <c r="C105" s="3"/>
+      <c r="B105" s="9"/>
+      <c r="C105" s="2"/>
     </row>
     <row r="106" spans="2:3" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B106" s="11"/>
-      <c r="C106" s="3"/>
+      <c r="B106" s="9"/>
+      <c r="C106" s="2"/>
     </row>
     <row r="107" spans="2:3" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B107" s="11"/>
-      <c r="C107" s="3"/>
+      <c r="B107" s="9"/>
+      <c r="C107" s="2"/>
     </row>
     <row r="108" spans="2:3" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B108" s="11"/>
-      <c r="C108" s="3"/>
-    </row>
-    <row r="109" spans="2:3" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B109" s="11"/>
-      <c r="C109" s="3"/>
-    </row>
-    <row r="110" spans="2:3" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B110" s="11"/>
-      <c r="C110" s="3"/>
-    </row>
-    <row r="111" spans="2:3" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B111" s="11"/>
-      <c r="C111" s="3"/>
-    </row>
-    <row r="112" spans="2:3" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B112" s="11"/>
-      <c r="C112" s="3"/>
-    </row>
+      <c r="B108" s="9"/>
+      <c r="C108" s="2"/>
+    </row>
+    <row r="109" spans="2:3" ht="16.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="110" spans="2:3" ht="16.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="111" spans="2:3" ht="16.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="112" spans="2:3" ht="16.5" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="113" ht="31.5" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="114" ht="32.25" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="115" ht="33" customHeight="1" x14ac:dyDescent="0.15"/>
@@ -995,39 +908,39 @@
     <row r="238" ht="32.25" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="239" ht="16.5" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="240" ht="31.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="241" ht="16.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="242" ht="31.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="243" ht="16.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="244" ht="16.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="245" ht="16.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="246" ht="16.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="247" ht="16.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="248" ht="16.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="249" ht="16.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="250" ht="16.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="251" ht="16.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="252" ht="16.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="253" ht="16.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="254" ht="16.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="255" ht="16.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="256" ht="16.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="257" spans="2:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="258" spans="2:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="259" spans="2:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B259" s="3"/>
-    </row>
-    <row r="260" spans="2:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B260" s="3"/>
-    </row>
-    <row r="261" spans="2:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B261" s="3"/>
-    </row>
-    <row r="262" spans="2:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B262" s="3"/>
-    </row>
+    <row r="241" spans="2:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="242" spans="2:2" ht="31.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="243" spans="2:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="244" spans="2:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="245" spans="2:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="246" spans="2:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="247" spans="2:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="248" spans="2:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="249" spans="2:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="250" spans="2:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="251" spans="2:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="252" spans="2:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="253" spans="2:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="254" spans="2:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="255" spans="2:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B255" s="2"/>
+    </row>
+    <row r="256" spans="2:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B256" s="2"/>
+    </row>
+    <row r="257" spans="2:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B257" s="2"/>
+    </row>
+    <row r="258" spans="2:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B258" s="2"/>
+    </row>
+    <row r="259" spans="2:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="260" spans="2:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="261" spans="2:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="262" spans="2:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.15"/>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="B84:B112"/>
+    <mergeCell ref="B80:B108"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
